--- a/Ujjivan-Connect-Task-Tracker.xlsx
+++ b/Ujjivan-Connect-Task-Tracker.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Done (6 Jul 2026): upload-time overlap detection in the CPMT Hub. On upload, the new document's chunks are compared against the ACTIVE corpus (one batched Qdrant query; chunk cosine &gt;= 0.80, candidate flagged at &gt;= 50% coverage). Strong overlaps pause the upload on a dedicated review page (/hub/documents/upload): each candidate shows % overlap with a severity label (near duplicate / strong / partial), clickable page chips open the existing PDF at the overlapping page, and 'Mark obsolete' retires superseded versions in the same action (Upload anyway / Cancel also available). Confirm reuses the cached parse+embeddings (no re-OCR/re-embed); the check fails open so a broken check never blocks uploads. Verified on the Deposit Policy version pair (V2.2 flagged at 84% when re-uploading V3.1). Testing surfaced 2 previously uncatalogued duplicates (Platina V3.0 double-ingest; NB36 copy of Deposit Policy V3.1) — added to docs/CORPUS-DUPLICATES.md. Out of scope: corpus-wide scan of already-ingested docs (cleanup stays manual per CORPUS-DUPLICATES.md).</t>
+          <t>Done (6 Jul 2026): upload-time overlap detection in the CPMT Hub. On upload, the new document's chunks are compared against the ACTIVE corpus (one batched Qdrant query; chunk cosine &gt;= 0.80, candidate flagged at &gt;= 50% coverage). Strong overlaps pause the upload on a dedicated review page (/hub/documents/upload): each candidate shows % overlap with a severity label (near duplicate / strong / partial), clickable page chips open the existing PDF at the overlapping page, and 'Mark obsolete' retires superseded versions in the same action (Upload anyway / Cancel also available). Confirm reuses the cached parse+embeddings (no re-OCR/re-embed); the check fails open so a broken check never blocks uploads. Verified on the Deposit Policy version pair (V2.2 flagged at 84% when re-uploading V3.1). Testing surfaced 2 previously uncatalogued duplicates (Platina V3.0 double-ingest; NB36 copy of Deposit Policy V3.1) — added to docs/CORPUS-DUPLICATES.md. Out of scope: corpus-wide scan of already-ingested docs (cleanup stays manual per CORPUS-DUPLICATES.md). Update (7 Jul 2026): side-by-side compare added to the overlap review — clicking a candidate's 'Compare side by side' button or any overlapping-page chip opens a split viewer with the just-picked upload on the left (rendered locally from the browser, before anything is stored) and the existing document on the right, opened at the matching page pair. A stepper walks both panes through every (upload page ↔ existing page) match reported by the backend; each pane keeps its own page/zoom controls. .docx uploads show a fallback in the left pane (browsers can't render Word).</t>
         </is>
       </c>
     </row>
